--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,33 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -451,23 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.72995</v>
+        <v>123.39167</v>
       </c>
       <c r="D2" t="n">
-        <v>16.11975</v>
+        <v>85.0398</v>
       </c>
       <c r="E2" t="n">
-        <v>16.24344</v>
+        <v>89.51712999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>21.83712</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.11565</v>
+        <v>508.36431</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61804</v>
+        <v>123.82337</v>
       </c>
       <c r="D3" t="n">
-        <v>15.81136</v>
+        <v>85.08441000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>16.17528</v>
+        <v>88.65589</v>
       </c>
       <c r="F3" t="n">
-        <v>21.52646</v>
-      </c>
-      <c r="G3" t="n">
-        <v>34.64045</v>
+        <v>516.2858</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.43964</v>
+        <v>120.70262</v>
       </c>
       <c r="D4" t="n">
-        <v>15.47726</v>
+        <v>85.92223</v>
       </c>
       <c r="E4" t="n">
-        <v>16.20864</v>
+        <v>90.41576000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>21.38675</v>
-      </c>
-      <c r="G4" t="n">
-        <v>33.58359</v>
+        <v>517.9508499999999</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +507,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.52637</v>
+        <v>121.29383</v>
       </c>
       <c r="D5" t="n">
-        <v>15.53254</v>
+        <v>86.02415999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>16.53437</v>
+        <v>91.99758</v>
       </c>
       <c r="F5" t="n">
-        <v>21.87574</v>
-      </c>
-      <c r="G5" t="n">
-        <v>33.40856</v>
+        <v>510.08068</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +526,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.85957</v>
+        <v>121.52247</v>
       </c>
       <c r="D6" t="n">
-        <v>15.60923</v>
+        <v>85.19432999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>16.26075</v>
+        <v>93.06373000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>21.55371</v>
-      </c>
-      <c r="G6" t="n">
-        <v>34.64576</v>
+        <v>516.27797</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75245</v>
+        <v>122.12975</v>
       </c>
       <c r="D7" t="n">
-        <v>16.30134</v>
+        <v>86.67158999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>16.33011</v>
+        <v>91.17816999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>21.86642</v>
-      </c>
-      <c r="G7" t="n">
-        <v>33.86405</v>
+        <v>509.63056</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62193</v>
+        <v>119.55174</v>
       </c>
       <c r="D8" t="n">
-        <v>16.00256</v>
+        <v>84.72626</v>
       </c>
       <c r="E8" t="n">
-        <v>16.43058</v>
+        <v>90.38451999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>21.70497</v>
-      </c>
-      <c r="G8" t="n">
-        <v>34.07868</v>
+        <v>515.2808</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.82587</v>
+        <v>120.6325</v>
       </c>
       <c r="D9" t="n">
-        <v>15.42276</v>
+        <v>86.50028</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8878</v>
+        <v>91.30186999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>21.5019</v>
-      </c>
-      <c r="G9" t="n">
-        <v>34.57867</v>
+        <v>514.13136</v>
       </c>
     </row>
     <row r="10">
@@ -631,50 +602,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.81421</v>
+        <v>121.41192</v>
       </c>
       <c r="D10" t="n">
-        <v>15.59669</v>
+        <v>85.03017</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16669</v>
+        <v>90.95573</v>
       </c>
       <c r="F10" t="n">
-        <v>21.22647</v>
-      </c>
-      <c r="G10" t="n">
-        <v>34.26195</v>
+        <v>500.77195</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Diameter</t>
         </is>
       </c>
     </row>
@@ -686,26 +634,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Micro Bump 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.53431</v>
+        <v>8.500450000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>16.78598</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.48811</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.10939</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05055</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.81691</v>
+        <v>23.94483</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +651,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.78342</v>
+        <v>8.69708</v>
       </c>
       <c r="D13" t="n">
-        <v>16.44003</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.84881</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.13859</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05031</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.79365</v>
+        <v>23.88367</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +664,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.2173</v>
+        <v>8.677</v>
       </c>
       <c r="D14" t="n">
-        <v>16.285</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.65448</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.08399</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.04968</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.82931</v>
+        <v>23.86217</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +677,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.08694</v>
+        <v>8.565720000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>16.54053</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.3704</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.05001</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05006</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.78093</v>
+        <v>24.34513</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +690,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.48939</v>
+        <v>8.64565</v>
       </c>
       <c r="D16" t="n">
-        <v>16.32173</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.33593</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.44893</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05042</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.80106</v>
+        <v>23.68397</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +703,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.68127</v>
+        <v>8.53945</v>
       </c>
       <c r="D17" t="n">
-        <v>16.54897</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.89358</v>
-      </c>
-      <c r="F17" t="n">
-        <v>42.22059</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.80951</v>
+        <v>24.11309</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +716,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.65437</v>
+        <v>8.538449999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>16.75005</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.56556</v>
-      </c>
-      <c r="F18" t="n">
-        <v>41.60448</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05038</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.80039</v>
+        <v>23.88392</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +729,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.73255</v>
+        <v>8.517200000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>16.26592</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.30867</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.33765</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.04964</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.80745</v>
+        <v>23.98831</v>
       </c>
     </row>
     <row r="20">
@@ -890,63 +742,41 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.60912</v>
+        <v>8.746790000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>16.61459</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.67217</v>
-      </c>
-      <c r="F20" t="n">
-        <v>41.95998</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05077</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.82765</v>
+        <v>24.45771</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -958,32 +788,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74056</v>
+        <v>16.58215</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08053</v>
+        <v>16.27896</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60317</v>
+        <v>16.39244</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95189</v>
+        <v>43.25941</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11069</v>
+        <v>0.04961</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09181</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12355</v>
+        <v>1.8053</v>
       </c>
     </row>
     <row r="23">
@@ -993,28 +817,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75474</v>
+        <v>17.11889</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07896</v>
+        <v>16.51498</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60294</v>
+        <v>16.58219</v>
       </c>
       <c r="F23" t="n">
-        <v>0.98033</v>
+        <v>42.79705</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1084</v>
+        <v>0.05045</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09247</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12675</v>
+        <v>1.80258</v>
       </c>
     </row>
     <row r="24">
@@ -1024,28 +842,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.73575</v>
+        <v>16.89806</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07947</v>
+        <v>16.50391</v>
       </c>
       <c r="E24" t="n">
-        <v>0.59919</v>
+        <v>16.65109</v>
       </c>
       <c r="F24" t="n">
-        <v>0.92774</v>
+        <v>41.59363</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10817</v>
+        <v>0.05116</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09211999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1248</v>
+        <v>1.79238</v>
       </c>
     </row>
     <row r="25">
@@ -1055,28 +867,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.74752</v>
+        <v>17.00746</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07882</v>
+        <v>16.44615</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6041800000000001</v>
+        <v>16.74438</v>
       </c>
       <c r="F25" t="n">
-        <v>0.94309</v>
+        <v>42.81017</v>
       </c>
       <c r="G25" t="n">
-        <v>0.107</v>
+        <v>0.05034</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09227</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12301</v>
+        <v>1.81231</v>
       </c>
     </row>
     <row r="26">
@@ -1086,28 +892,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7405</v>
+        <v>16.94224</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08021</v>
+        <v>16.03936</v>
       </c>
       <c r="E26" t="n">
-        <v>0.59805</v>
+        <v>16.49349</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95208</v>
+        <v>42.42684</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10765</v>
+        <v>0.05044</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09415999999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12348</v>
+        <v>1.78016</v>
       </c>
     </row>
     <row r="27">
@@ -1117,28 +917,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.72444</v>
+        <v>16.70233</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08066</v>
+        <v>16.58395</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60685</v>
+        <v>16.67257</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95408</v>
+        <v>42.26083</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11</v>
+        <v>0.05073</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09079</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.1277</v>
+        <v>1.84259</v>
       </c>
     </row>
     <row r="28">
@@ -1148,28 +942,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.73559</v>
+        <v>16.97666</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07951999999999999</v>
+        <v>16.40302</v>
       </c>
       <c r="E28" t="n">
-        <v>0.60304</v>
+        <v>16.59317</v>
       </c>
       <c r="F28" t="n">
-        <v>0.94897</v>
+        <v>41.58063</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1095</v>
+        <v>0.0503</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00752</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09227</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12899</v>
+        <v>1.80877</v>
       </c>
     </row>
     <row r="29">
@@ -1179,28 +967,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74058</v>
+        <v>16.85749</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08042000000000001</v>
+        <v>16.03069</v>
       </c>
       <c r="E29" t="n">
-        <v>0.59322</v>
+        <v>16.65521</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95608</v>
+        <v>42.1869</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10917</v>
+        <v>0.05141</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00752</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09261999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12427</v>
+        <v>1.80834</v>
       </c>
     </row>
     <row r="30">
@@ -1210,28 +992,348 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.73141</v>
+        <v>16.65948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07899</v>
+        <v>16.27491</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60136</v>
+        <v>16.32819</v>
       </c>
       <c r="F30" t="n">
-        <v>0.95646</v>
+        <v>42.48547</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11203</v>
+        <v>0.05052</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09118999999999999</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12773</v>
+        <v>1.81867</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.75221</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.60428</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11003</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09161999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12325</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7394500000000001</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6089</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.96921</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11036</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09271</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12515</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.74835</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08071</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.59992</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.97956</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10798</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09234000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12668</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74078</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.60823</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96565</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10956</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09141000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12399</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.74738</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08187</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.60447</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.96249</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10854</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00746</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.1242</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.74555</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.07968</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61637</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.94757</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09232</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1268</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.74519</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.07908</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6132300000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9341699999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09336999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1258</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7393999999999999</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08062999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.59892</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10756</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12437</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.73262</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08118</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.95313</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10954</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09442</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12428</v>
       </c>
     </row>
   </sheetData>
